--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/SIM_XA_FIXED订单详情.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/SIM_XA_FIXED订单详情.xlsx
@@ -1111,7 +1111,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED10</t>
+          <t>SIM_XA_FIXED23</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED02</t>
+          <t>SIM_XA_FIXED26</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED06</t>
+          <t>SIM_XA_FIXED19</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED22</t>
+          <t>SIM_XA_FIXED16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED14</t>
+          <t>SIM_XA_FIXED24</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED20</t>
+          <t>SIM_XA_FIXED05</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED19</t>
+          <t>SIM_XA_FIXED25</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED09</t>
+          <t>SIM_XA_FIXED18</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED15</t>
+          <t>SIM_XA_FIXED20</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED12</t>
+          <t>SIM_XA_FIXED08</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED25</t>
+          <t>SIM_XA_FIXED06</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED21</t>
+          <t>SIM_XA_FIXED11</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED24</t>
+          <t>SIM_XA_FIXED03</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED13</t>
+          <t>SIM_XA_FIXED12</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED23</t>
+          <t>SIM_XA_FIXED14</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED11</t>
+          <t>SIM_XA_FIXED18</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED10</t>
+          <t>SIM_XA_FIXED25</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED05</t>
+          <t>SIM_XA_FIXED27</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED08</t>
+          <t>SIM_XA_FIXED18</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED14</t>
+          <t>SIM_XA_FIXED24</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED25</t>
+          <t>SIM_XA_FIXED10</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED27</t>
+          <t>SIM_XA_FIXED06</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -11747,14 +11747,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED26</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>已交</t>
+          <t>未分配</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12412,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED13</t>
+          <t>SIM_XA_FIXED17</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -12516,7 +12511,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED09</t>
+          <t>SIM_XA_FIXED12</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -13931,7 +13926,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED16</t>
+          <t>SIM_XA_FIXED02</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -15205,7 +15200,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED23</t>
+          <t>SIM_XA_FIXED22</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -16479,7 +16474,7 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED04</t>
+          <t>SIM_XA_FIXED07</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -16860,7 +16855,7 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED15</t>
+          <t>SIM_XA_FIXED24</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -17570,7 +17565,7 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED01</t>
+          <t>SIM_XA_FIXED19</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -17669,7 +17664,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED12</t>
+          <t>SIM_XA_FIXED09</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -17721,7 +17716,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED22</t>
+          <t>SIM_XA_FIXED26</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -17820,7 +17815,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED16</t>
+          <t>SIM_XA_FIXED22</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -18436,7 +18431,7 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED24</t>
+          <t>SIM_XA_FIXED05</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -18723,7 +18718,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED24</t>
+          <t>SIM_XA_FIXED19</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -18963,7 +18958,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED02</t>
+          <t>SIM_XA_FIXED07</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -19814,7 +19809,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED06</t>
+          <t>SIM_XA_FIXED20</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -19913,7 +19908,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED21</t>
+          <t>SIM_XA_FIXED06</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -20527,14 +20522,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED10</t>
-        </is>
-      </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>已交</t>
+          <t>未分配</t>
         </is>
       </c>
     </row>
@@ -21568,7 +21558,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED20</t>
+          <t>SIM_XA_FIXED27</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -22090,7 +22080,7 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED21</t>
+          <t>SIM_XA_FIXED13</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -22424,7 +22414,7 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED17</t>
+          <t>SIM_XA_FIXED21</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
@@ -23040,7 +23030,7 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED14</t>
+          <t>SIM_XA_FIXED03</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -23233,7 +23223,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED04</t>
+          <t>SIM_XA_FIXED16</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -24317,9 +24307,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>SIM_XA_FIXED01</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>未分配</t>
+          <t>已交</t>
         </is>
       </c>
     </row>
@@ -24460,7 +24455,7 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED18</t>
+          <t>SIM_XA_FIXED23</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -25452,7 +25447,7 @@
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED06</t>
+          <t>SIM_XA_FIXED11</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -26442,14 +26437,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED14</t>
-        </is>
-      </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>已交</t>
+          <t>未分配</t>
         </is>
       </c>
     </row>
